--- a/Compititor's_Price/IKO_Prices/IKO_Prices_01-10-2025.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_01-10-2025.xlsx
@@ -498,17 +498,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.97</t>
+          <t>£10.87</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.97</t>
+          <t>£10.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.97</t>
+          <t>£10.87</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,17 +555,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.57</t>
+          <t>£12.39</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.57</t>
+          <t>£12.39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.57</t>
+          <t>£12.39</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£16.01</t>
+          <t>£15.86</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£16.01</t>
+          <t>£15.86</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£16.01</t>
+          <t>£15.86</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -669,17 +669,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£16.28</t>
+          <t>£16.17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£16.28</t>
+          <t>£16.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£16.28</t>
+          <t>£16.17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£20.79</t>
+          <t>£20.58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£20.79</t>
+          <t>£20.58</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£20.79</t>
+          <t>£20.58</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£22.79</t>
+          <t>£22.52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£22.79</t>
+          <t>£22.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£22.79</t>
+          <t>£22.52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£23.00</t>
+          <t>£22.68</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£23.00</t>
+          <t>£22.68</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£23.00</t>
+          <t>£22.68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£26.41</t>
+          <t>£26.10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£26.41</t>
+          <t>£26.10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£26.41</t>
+          <t>£26.10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£28.61</t>
+          <t>£28.30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£28.61</t>
+          <t>£28.30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£28.61</t>
+          <t>£28.30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£28.13</t>
+          <t>£27.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£28.13</t>
+          <t>£27.83</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£28.13</t>
+          <t>£27.83</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1068,17 +1068,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£37.33</t>
+          <t>£36.89</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£37.33</t>
+          <t>£36.89</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£37.33</t>
+          <t>£36.89</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1125,17 +1125,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£34.53</t>
+          <t>£34.11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£34.53</t>
+          <t>£34.11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£34.53</t>
+          <t>£34.11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£43.00</t>
+          <t>£42.41</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£43.00</t>
+          <t>£42.41</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£43.00</t>
+          <t>£42.41</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1239,17 +1239,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£42.89</t>
+          <t>£42.47</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£42.89</t>
+          <t>£42.47</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£42.89</t>
+          <t>£42.47</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
